--- a/PUEYRREDON 1494/Octubre/PUEYRREDON Octubre.xlsx
+++ b/PUEYRREDON 1494/Octubre/PUEYRREDON Octubre.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PUEYRREDON 1494\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PUEYRREDON 1494\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C81F52F-A560-4D03-943F-005ACFF39144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E7D1BA-CD67-497B-B5CB-B906105CCE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$113</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$110</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="161">
   <si>
     <t>MAIL: consorciopueyrredon1494@gmail.com</t>
   </si>
@@ -180,9 +180,6 @@
     <t>Ingreso</t>
   </si>
   <si>
-    <t>Depisitos ya identificados</t>
-  </si>
-  <si>
     <t xml:space="preserve">Deposito sin identificar </t>
   </si>
   <si>
@@ -453,70 +450,64 @@
     <t>Las expensas deberán abonarse en el Banco Comafi. Cuenta Corriente en pesos.                                                                                                                                                               Número 0240-00485/3 CUIT: 30-68041540-0 a nombre del Con. De Prop. C Pueyrredon 1494 - CBU 2990024602400048530006</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
     <t>Limpieza marquesina</t>
   </si>
   <si>
     <t>DEPOSITA SIEMPRE VALERIA</t>
   </si>
   <si>
-    <t>SUBIDOS EN JULI</t>
-  </si>
-  <si>
     <t xml:space="preserve">Punitorios mal cobrados </t>
   </si>
   <si>
     <t>Lourdes</t>
   </si>
   <si>
-    <t>Deposito ya identificado del mes anterior</t>
-  </si>
-  <si>
-    <t>VTO 15/10</t>
-  </si>
-  <si>
-    <t>PERÍODO: SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>Mes de SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>Mantenimiento Ascensores - Mes de SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>Transf 11/09</t>
-  </si>
-  <si>
-    <t>Reliquidacion de deuda de unidades funcionales - Mateo Quotteri</t>
-  </si>
-  <si>
-    <t>Debito 12/09</t>
-  </si>
-  <si>
-    <t>PMC 12/09</t>
-  </si>
-  <si>
-    <t>Debito 30/09</t>
-  </si>
-  <si>
-    <t>No se debito</t>
-  </si>
-  <si>
-    <t>Transf 30/09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7/9 arreglo terraza Sr. Luis (Total a abonar $1.250.000) </t>
-  </si>
-  <si>
     <t>Yamil Martinez</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>VTO 14/11</t>
+  </si>
+  <si>
+    <t>PERÍODO: OCTUBRE</t>
+  </si>
+  <si>
+    <t>Mes de OCTUBRE</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de OCTUBRE</t>
+  </si>
+  <si>
+    <t>Mantenimiento Ascensores - Mes de OCTUBRE</t>
+  </si>
+  <si>
+    <t>SUBIDOS EN 0CT</t>
+  </si>
+  <si>
+    <t>PMC 08/10</t>
+  </si>
+  <si>
+    <t>Debito 14/10</t>
+  </si>
+  <si>
+    <t>Transf 14/10</t>
+  </si>
+  <si>
+    <t>Debito 21/10</t>
+  </si>
+  <si>
+    <t>Reparacion de bobas elevadoras n2, modificacion de cañeria para la colocacion de dos valvulas de retencion - mano de obra y materiales</t>
+  </si>
+  <si>
+    <t>Transf 21/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/9 arreglo terraza Sr. Luis (Total a abonar $1.250.000) </t>
+  </si>
+  <si>
+    <t>PAULA</t>
   </si>
 </sst>
 </file>
@@ -1199,7 +1190,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1403,12 +1394,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1480,6 +1468,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1835,7 +1824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M117"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -1901,7 +1890,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="135" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C6" s="135"/>
       <c r="D6" s="136" t="s">
@@ -1919,52 +1908,52 @@
       <c r="E7" s="149"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="157" t="s">
-        <v>149</v>
-      </c>
-      <c r="C9" s="158"/>
+      <c r="B9" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" s="155"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="158"/>
-      <c r="C10" s="158"/>
+      <c r="B10" s="155"/>
+      <c r="C10" s="155"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="158"/>
-      <c r="C11" s="158"/>
+      <c r="B11" s="155"/>
+      <c r="C11" s="155"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" s="132"/>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="161" t="s">
+      <c r="A14" s="158" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="158"/>
-      <c r="C14" s="158"/>
-      <c r="D14" s="158"/>
-      <c r="E14" s="158"/>
+      <c r="B14" s="155"/>
+      <c r="C14" s="155"/>
+      <c r="D14" s="155"/>
+      <c r="E14" s="155"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="158"/>
-      <c r="B15" s="158"/>
-      <c r="C15" s="158"/>
-      <c r="D15" s="158"/>
-      <c r="E15" s="158"/>
+      <c r="A15" s="155"/>
+      <c r="B15" s="155"/>
+      <c r="C15" s="155"/>
+      <c r="D15" s="155"/>
+      <c r="E15" s="155"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="158"/>
-      <c r="B16" s="158"/>
-      <c r="C16" s="158"/>
-      <c r="D16" s="158"/>
-      <c r="E16" s="158"/>
+      <c r="A16" s="155"/>
+      <c r="B16" s="155"/>
+      <c r="C16" s="155"/>
+      <c r="D16" s="155"/>
+      <c r="E16" s="155"/>
     </row>
     <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="158"/>
-      <c r="B17" s="158"/>
-      <c r="C17" s="158"/>
-      <c r="D17" s="158"/>
-      <c r="E17" s="158"/>
+      <c r="A17" s="155"/>
+      <c r="B17" s="155"/>
+      <c r="C17" s="155"/>
+      <c r="D17" s="155"/>
+      <c r="E17" s="155"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -1995,8 +1984,8 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="154">
-        <v>870928.3</v>
+      <c r="D23" s="120">
+        <v>884884.9</v>
       </c>
       <c r="E23" s="80"/>
     </row>
@@ -2006,8 +1995,8 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="154">
-        <v>-189426.91</v>
+      <c r="D24" s="120">
+        <v>-192462.47</v>
       </c>
       <c r="E24" s="80"/>
     </row>
@@ -2017,9 +2006,7 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="154">
-        <v>0.61</v>
-      </c>
+      <c r="D25" s="120"/>
       <c r="E25" s="80"/>
       <c r="H25" s="15"/>
     </row>
@@ -2039,7 +2026,7 @@
       <c r="C27" s="57"/>
       <c r="D27" s="121">
         <f>SUM(D23:D26)</f>
-        <v>681502</v>
+        <v>692422.43</v>
       </c>
       <c r="E27" s="81"/>
       <c r="H27" s="5"/>
@@ -2081,7 +2068,7 @@
       <c r="D31" s="122"/>
       <c r="E31" s="82">
         <f>D27+D30</f>
-        <v>681502</v>
+        <v>692422.43</v>
       </c>
       <c r="F31" s="15"/>
     </row>
@@ -2099,747 +2086,728 @@
         <v>18</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C33" s="5"/>
-      <c r="D33" s="154">
-        <v>40000</v>
+      <c r="D33" s="120">
+        <v>39000</v>
       </c>
       <c r="E33" s="84"/>
     </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="64" t="s">
-        <v>155</v>
-      </c>
-      <c r="B34" s="5"/>
+    <row r="34" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>149</v>
+      </c>
       <c r="C34" s="5"/>
-      <c r="D34" s="154">
-        <v>130000</v>
+      <c r="D34" s="120">
+        <v>143100</v>
       </c>
       <c r="E34" s="84"/>
+      <c r="H34" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="154">
-        <v>135100</v>
-      </c>
-      <c r="E35" s="84"/>
-      <c r="H35" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="23" t="s">
+      <c r="A35" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="124"/>
-      <c r="E36" s="85">
-        <f>SUM(D33:D35)</f>
-        <v>305100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="30" t="s">
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="124"/>
+      <c r="E35" s="85">
+        <f>SUM(D33:D34)</f>
+        <v>182100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="125"/>
-      <c r="E37" s="66"/>
-    </row>
-    <row r="38" spans="1:8" s="36" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="162" t="s">
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="125"/>
+      <c r="E36" s="66"/>
+    </row>
+    <row r="37" spans="1:8" s="36" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="159" t="s">
         <v>22</v>
       </c>
-      <c r="B38" s="160"/>
+      <c r="B37" s="157"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="153">
+        <v>87562.7</v>
+      </c>
+      <c r="E37" s="106"/>
+    </row>
+    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="159" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" s="157"/>
       <c r="C38" s="55"/>
-      <c r="D38" s="155">
-        <v>87562.7</v>
+      <c r="D38" s="126">
+        <v>6646.91</v>
       </c>
       <c r="E38" s="106"/>
     </row>
-    <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="162" t="s">
-        <v>23</v>
-      </c>
-      <c r="B39" s="160"/>
-      <c r="C39" s="55"/>
-      <c r="D39" s="153">
-        <v>6646.91</v>
-      </c>
-      <c r="E39" s="106"/>
-    </row>
-    <row r="40" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="23" t="s">
+    <row r="39" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="124"/>
-      <c r="E40" s="86">
-        <f>SUM(D38:D39)</f>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="124"/>
+      <c r="E39" s="86">
+        <f>SUM(D37:D38)</f>
         <v>94209.61</v>
       </c>
     </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="127"/>
+      <c r="E40" s="87"/>
+    </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="127"/>
-      <c r="E41" s="87"/>
+      <c r="A41" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="126">
+        <v>417913.51</v>
+      </c>
+      <c r="E41" s="107" t="s">
+        <v>153</v>
+      </c>
+      <c r="G41" s="104"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="53"/>
-      <c r="D42" s="153">
-        <v>385570.28</v>
-      </c>
-      <c r="E42" s="107" t="s">
-        <v>157</v>
-      </c>
-      <c r="G42" s="104"/>
+        <v>150</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="126">
+        <v>21773.200000000001</v>
+      </c>
+      <c r="E42" s="108" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>152</v>
+      <c r="A43" s="5" t="str">
+        <f>A42</f>
+        <v>Sindicatos mes de OCTUBRE</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="153">
-        <v>19965.03</v>
-      </c>
-      <c r="E43" s="108" t="s">
-        <v>156</v>
+      <c r="D43" s="126">
+        <v>69320.33</v>
+      </c>
+      <c r="E43" s="108" t="str">
+        <f>E42</f>
+        <v>Debito 14/10</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="str">
         <f>A43</f>
-        <v>Sindicatos mes de SEPTIEMBRE</v>
+        <v>Sindicatos mes de OCTUBRE</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="153">
-        <v>64395.09</v>
-      </c>
-      <c r="E44" s="108" t="str">
+      <c r="D44" s="126">
+        <v>4354.6400000000003</v>
+      </c>
+      <c r="E44" s="109" t="str">
         <f>E43</f>
-        <v>Debito 12/09</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="str">
-        <f>A44</f>
-        <v>Sindicatos mes de SEPTIEMBRE</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="153">
-        <v>3993.01</v>
-      </c>
-      <c r="E45" s="109" t="str">
-        <f>E44</f>
-        <v>Debito 12/09</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="23" t="s">
+        <v>Debito 14/10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="23" t="s">
         <v>30</v>
+      </c>
+      <c r="B45" s="24"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="128"/>
+      <c r="E45" s="86">
+        <f>SUM(D41:D44)</f>
+        <v>513361.68000000005</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="32" t="s">
+        <v>31</v>
       </c>
       <c r="B46" s="24"/>
       <c r="C46" s="24"/>
-      <c r="D46" s="128"/>
-      <c r="E46" s="86">
-        <f>SUM(D42:D45)</f>
-        <v>473923.41000000003</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B47" s="24"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="127"/>
-      <c r="E47" s="87"/>
+      <c r="D46" s="127"/>
+      <c r="E46" s="87"/>
+    </row>
+    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="126">
+        <v>46850</v>
+      </c>
+      <c r="E47" s="90" t="s">
+        <v>155</v>
+      </c>
+      <c r="G47" s="112"/>
     </row>
     <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="53" t="s">
-        <v>153</v>
+      <c r="A48" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="153">
-        <v>44625</v>
+      <c r="D48" s="126">
+        <f>193135.96-102510.59</f>
+        <v>90625.37</v>
       </c>
       <c r="E48" s="90" t="s">
-        <v>154</v>
-      </c>
-      <c r="G48" s="112"/>
-    </row>
-    <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="153">
-        <v>102510.59</v>
+      <c r="D49" s="126">
+        <v>24334.720000000001</v>
       </c>
       <c r="E49" s="90" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="126" t="s">
-        <v>159</v>
-      </c>
-      <c r="E50" s="90"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="153">
-        <v>35000</v>
+      <c r="D50" s="126">
+        <v>40000</v>
+      </c>
+      <c r="E50" s="90" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="156" t="s">
+        <v>157</v>
+      </c>
+      <c r="B51" s="157"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="185">
+        <v>640000</v>
       </c>
       <c r="E51" s="90" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="159" t="s">
-        <v>142</v>
-      </c>
-      <c r="B52" s="160"/>
-      <c r="C52" s="56"/>
-      <c r="D52" s="156">
-        <v>71000</v>
-      </c>
-      <c r="E52" s="90" t="s">
-        <v>160</v>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B52" s="23"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="124"/>
+      <c r="E52" s="86">
+        <f>SUM(D47:D51)</f>
+        <v>841810.09</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="23" t="s">
-        <v>34</v>
+      <c r="A53" s="32" t="s">
+        <v>35</v>
       </c>
       <c r="B53" s="23"/>
       <c r="C53" s="23"/>
       <c r="D53" s="124"/>
-      <c r="E53" s="86">
-        <f>SUM(D48:D52)</f>
-        <v>253135.59</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="B54" s="23"/>
-      <c r="C54" s="23"/>
-      <c r="D54" s="124"/>
-      <c r="E54" s="89"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="53"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="88"/>
+      <c r="E53" s="89"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="53"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="88"/>
+    </row>
+    <row r="55" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="92">
+        <f>SUM(D54:D54)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B56" s="32"/>
-      <c r="C56" s="32"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="92">
-        <f>SUM(D55:D55)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="32" t="s">
+      <c r="A56" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="B57" s="65"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="122"/>
-      <c r="E57" s="89"/>
+      <c r="B56" s="65"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="122"/>
+      <c r="E56" s="89"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="126">
+        <v>47641.06</v>
+      </c>
+      <c r="E57" s="93"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="153">
-        <v>40649.81</v>
-      </c>
-      <c r="E58" s="93"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="153">
+      <c r="D58" s="126">
         <v>56000</v>
       </c>
-      <c r="E59" s="91"/>
+      <c r="E58" s="91"/>
+    </row>
+    <row r="59" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="52" t="s">
+        <v>20</v>
+      </c>
+      <c r="B59" s="52"/>
+      <c r="C59" s="52"/>
+      <c r="D59" s="94"/>
+      <c r="E59" s="86">
+        <f>SUM(D57:D58)</f>
+        <v>103641.06</v>
+      </c>
     </row>
     <row r="60" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="B60" s="52"/>
-      <c r="C60" s="52"/>
-      <c r="D60" s="94"/>
-      <c r="E60" s="86">
-        <f>SUM(D58:D59)</f>
-        <v>96649.81</v>
-      </c>
+      <c r="A60" s="5"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="80"/>
+      <c r="E60" s="95"/>
     </row>
     <row r="61" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="5"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="80"/>
-      <c r="E61" s="95"/>
+      <c r="A61" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" s="25"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="96"/>
+      <c r="E61" s="97">
+        <f>4000000-1904520.42-523024.45</f>
+        <v>1572455.1300000001</v>
+      </c>
     </row>
     <row r="62" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="25"/>
-      <c r="C62" s="25"/>
-      <c r="D62" s="96"/>
-      <c r="E62" s="97">
-        <f>4000000-1904520.42</f>
-        <v>2095479.58</v>
-      </c>
+      <c r="A62" s="1"/>
+      <c r="D62" s="98"/>
+      <c r="E62" s="99"/>
+      <c r="F62" s="43"/>
     </row>
     <row r="63" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="1"/>
-      <c r="D63" s="98"/>
-      <c r="E63" s="99"/>
+      <c r="A63" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" s="10"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="100"/>
+      <c r="E63" s="101">
+        <f>(SUM(E31:E61))</f>
+        <v>4000000</v>
+      </c>
       <c r="F63" s="43"/>
-    </row>
-    <row r="64" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="10"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="100"/>
-      <c r="E64" s="101">
-        <f>(SUM(E31:E62))</f>
-        <v>4000000</v>
-      </c>
-      <c r="F64" s="43"/>
+      <c r="G63" s="112"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D64" s="98"/>
+      <c r="E64" s="98"/>
       <c r="G64" s="112"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D65" s="98"/>
       <c r="E65" s="98"/>
-      <c r="G65" s="112"/>
-    </row>
-    <row r="66" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D66" s="98"/>
-      <c r="E66" s="98"/>
-    </row>
-    <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="11" t="s">
+    </row>
+    <row r="66" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B67" s="12"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="102"/>
-      <c r="E67" s="103"/>
-    </row>
-    <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="159" t="s">
-        <v>161</v>
-      </c>
-      <c r="B68" s="165"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="169">
+      <c r="B66" s="12"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="102"/>
+      <c r="E66" s="103"/>
+    </row>
+    <row r="67" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="156" t="s">
+        <v>159</v>
+      </c>
+      <c r="B67" s="162"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="166">
         <v>181000</v>
       </c>
-      <c r="E68" s="171"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="166"/>
-      <c r="B69" s="167"/>
+      <c r="E67" s="168"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="163"/>
+      <c r="B68" s="164"/>
+      <c r="C68" s="53"/>
+      <c r="D68" s="167"/>
+      <c r="E68" s="169"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="156"/>
+      <c r="B69" s="157"/>
       <c r="C69" s="53"/>
-      <c r="D69" s="170"/>
-      <c r="E69" s="172"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="159"/>
-      <c r="B70" s="160"/>
-      <c r="C70" s="53"/>
-      <c r="D70" s="34"/>
-      <c r="E70" s="130"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="50"/>
-      <c r="B71" s="49"/>
-      <c r="C71" s="49"/>
-      <c r="D71" s="58"/>
-      <c r="E71" s="152">
-        <f>SUM(D68:D70)</f>
+      <c r="D69" s="34"/>
+      <c r="E69" s="130"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="50"/>
+      <c r="B70" s="49"/>
+      <c r="C70" s="49"/>
+      <c r="D70" s="58"/>
+      <c r="E70" s="152">
+        <f>SUM(D67:D69)</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="25" t="s">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B73" s="25"/>
-      <c r="C73" s="25"/>
-      <c r="D73" s="26"/>
-      <c r="E73" s="113"/>
-    </row>
-    <row r="74" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="75" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="3" t="s">
+      <c r="B72" s="25"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="26"/>
+      <c r="E72" s="113"/>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B75" s="10"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="67">
-        <f>E71+E73</f>
+      <c r="B74" s="10"/>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="67">
+        <f>E70+E72</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="77" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="78" t="s">
+        <v>44</v>
+      </c>
+      <c r="B76" s="79">
+        <f>E63</f>
+        <v>4000000</v>
+      </c>
+      <c r="D76" s="43"/>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="78" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B77" s="79">
-        <f>E64</f>
-        <v>4000000</v>
-      </c>
-      <c r="D77" s="43"/>
-    </row>
-    <row r="78" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <f>E63-E61</f>
+        <v>2427544.87</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="78" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B78" s="79">
-        <f>E64-E62</f>
-        <v>1904520.42</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <f>E74-E72</f>
+        <v>181000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="78" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B79" s="79">
-        <f>E75-E73</f>
+        <f>E74</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="78" t="s">
-        <v>47</v>
-      </c>
-      <c r="B80" s="79">
-        <f>E75</f>
-        <v>181000</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="160"/>
+      <c r="B82" s="155"/>
+      <c r="C82" s="155"/>
+      <c r="D82" s="155"/>
+      <c r="E82" s="155"/>
+    </row>
     <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="163"/>
-      <c r="B83" s="158"/>
-      <c r="C83" s="158"/>
-      <c r="D83" s="158"/>
-      <c r="E83" s="158"/>
-    </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="158"/>
-      <c r="B84" s="158"/>
-      <c r="C84" s="158"/>
-      <c r="D84" s="158"/>
-      <c r="E84" s="158"/>
-    </row>
-    <row r="85" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="158"/>
-      <c r="B85" s="158"/>
-      <c r="C85" s="158"/>
-      <c r="D85" s="158"/>
-      <c r="E85" s="158"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="16" t="s">
+      <c r="A83" s="155"/>
+      <c r="B83" s="155"/>
+      <c r="C83" s="155"/>
+      <c r="D83" s="155"/>
+      <c r="E83" s="155"/>
+    </row>
+    <row r="84" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="155"/>
+      <c r="B84" s="155"/>
+      <c r="C84" s="155"/>
+      <c r="D84" s="155"/>
+      <c r="E84" s="155"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B87" s="38"/>
-      <c r="C87" s="17"/>
-    </row>
-    <row r="88" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="28" t="s">
+      <c r="B86" s="38"/>
+      <c r="C86" s="17"/>
+    </row>
+    <row r="87" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="B88" s="111">
-        <v>-421384.30749999965</v>
-      </c>
-      <c r="C88" s="19"/>
-    </row>
-    <row r="89" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="18" t="s">
+      <c r="B87" s="111">
+        <v>223239.20250000013</v>
+      </c>
+      <c r="C87" s="19"/>
+    </row>
+    <row r="88" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="B89" s="39">
+      <c r="B88" s="39">
         <f>PRORRATEO!H25</f>
-        <v>2730143.9299999997</v>
+        <v>4082670.82</v>
+      </c>
+      <c r="C88" s="17"/>
+    </row>
+    <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="150" t="s">
+        <v>143</v>
+      </c>
+      <c r="B89" s="47">
+        <f>-10418-23580</f>
+        <v>-33998</v>
       </c>
       <c r="C89" s="17"/>
     </row>
-    <row r="90" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B90" s="47"/>
+      <c r="B90" s="91">
+        <f>B109</f>
+        <v>0</v>
+      </c>
       <c r="C90" s="17"/>
     </row>
-    <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="150" t="s">
-        <v>146</v>
-      </c>
-      <c r="B91" s="47"/>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="B91" s="47">
+        <f>-B77</f>
+        <v>-2427544.87</v>
+      </c>
       <c r="C91" s="17"/>
     </row>
-    <row r="92" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="150" t="s">
-        <v>148</v>
-      </c>
-      <c r="B92" s="47"/>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B92" s="47">
+        <f>-(B78)</f>
+        <v>-181000</v>
+      </c>
       <c r="C92" s="17"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="18" t="s">
+      <c r="A93" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B93" s="110">
+        <f>SUM(B87:B92)</f>
+        <v>1663367.1524999999</v>
+      </c>
+      <c r="C93" s="20"/>
+    </row>
+    <row r="94" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B94" s="40"/>
+      <c r="C94" s="20"/>
+      <c r="D94" s="43"/>
+    </row>
+    <row r="95" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B95" s="41"/>
+      <c r="C95" s="20"/>
+    </row>
+    <row r="96" spans="1:5" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="40"/>
+      <c r="C96" s="35"/>
+    </row>
+    <row r="97" spans="1:13" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B97" s="33"/>
+      <c r="C97" s="35"/>
+      <c r="D97" s="46"/>
+    </row>
+    <row r="98" spans="1:13" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B98" s="34">
+        <v>0</v>
+      </c>
+      <c r="C98" s="35"/>
+    </row>
+    <row r="99" spans="1:13" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B99" s="33">
+        <v>0</v>
+      </c>
+      <c r="C99" s="20"/>
+      <c r="D99" s="43"/>
+    </row>
+    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B93" s="91">
-        <f>B112</f>
+      <c r="B100" s="33">
         <v>0</v>
       </c>
-      <c r="C93" s="17"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="37" t="s">
+      <c r="C100" s="20"/>
+    </row>
+    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B94" s="47">
-        <f>-B78</f>
-        <v>-1904520.42</v>
-      </c>
-      <c r="C94" s="17"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B95" s="47">
-        <f>-(B79)</f>
-        <v>-181000</v>
-      </c>
-      <c r="C95" s="17"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="27" t="s">
+      <c r="B101" s="33">
+        <v>0</v>
+      </c>
+      <c r="C101" s="22"/>
+    </row>
+    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B102" s="48">
+        <f>SUM(B98:B101)</f>
+        <v>0</v>
+      </c>
+      <c r="C102" s="17"/>
+    </row>
+    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="1:13" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" s="161" t="s">
+        <v>57</v>
+      </c>
+      <c r="B105" s="155"/>
+      <c r="C105" s="155"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" s="155"/>
+      <c r="B106" s="155"/>
+      <c r="C106" s="155"/>
+    </row>
+    <row r="107" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="55"/>
+      <c r="B107" s="33"/>
+      <c r="C107" s="33">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="55"/>
+      <c r="B108" s="33"/>
+      <c r="C108" s="40"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="B96" s="110">
-        <f>SUM(B88:B95)</f>
-        <v>223239.20250000013</v>
-      </c>
-      <c r="C96" s="20"/>
-    </row>
-    <row r="97" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="40"/>
-      <c r="C97" s="20"/>
-      <c r="D97" s="43"/>
-    </row>
-    <row r="98" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B98" s="41"/>
-      <c r="C98" s="20"/>
-    </row>
-    <row r="99" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="40"/>
-      <c r="C99" s="35"/>
-    </row>
-    <row r="100" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="B100" s="33"/>
-      <c r="C100" s="35"/>
-      <c r="D100" s="46"/>
-    </row>
-    <row r="101" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B101" s="34">
+      <c r="B109" s="105">
+        <f>SUM(B107:B108)</f>
         <v>0</v>
       </c>
-      <c r="C101" s="35"/>
-    </row>
-    <row r="102" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B102" s="33">
-        <v>0</v>
-      </c>
-      <c r="C102" s="20"/>
-      <c r="D102" s="43"/>
-    </row>
-    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B103" s="33">
-        <v>0</v>
-      </c>
-      <c r="C103" s="20"/>
-    </row>
-    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B104" s="33">
-        <v>0</v>
-      </c>
-      <c r="C104" s="22"/>
-    </row>
-    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="B105" s="48">
-        <f>SUM(B101:B104)</f>
-        <v>0</v>
-      </c>
-      <c r="C105" s="17"/>
-    </row>
-    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="1:4" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="164" t="s">
-        <v>58</v>
-      </c>
-      <c r="B108" s="158"/>
-      <c r="C108" s="158"/>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="158"/>
-      <c r="B109" s="158"/>
-      <c r="C109" s="158"/>
-    </row>
-    <row r="110" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="55"/>
-      <c r="B110" s="33"/>
-      <c r="C110" s="33">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="55"/>
-      <c r="B111" s="33"/>
-      <c r="C111" s="40"/>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="B112" s="105">
-        <f>SUM(B110:B111)</f>
-        <v>0</v>
-      </c>
-      <c r="C112" s="45"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M113" s="8"/>
-    </row>
-    <row r="114" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="168"/>
-      <c r="B114" s="158"/>
-      <c r="C114" s="158"/>
-      <c r="D114" s="158"/>
-      <c r="E114" s="158"/>
-    </row>
-    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="158"/>
-      <c r="B115" s="158"/>
-      <c r="C115" s="158"/>
-      <c r="D115" s="158"/>
-      <c r="E115" s="158"/>
-    </row>
-    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="158"/>
-      <c r="B116" s="158"/>
-      <c r="C116" s="158"/>
-      <c r="D116" s="158"/>
-      <c r="E116" s="158"/>
-    </row>
-    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="158"/>
-      <c r="B117" s="158"/>
-      <c r="C117" s="158"/>
-      <c r="D117" s="158"/>
-      <c r="E117" s="158"/>
+      <c r="C109" s="45"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M110" s="8"/>
+    </row>
+    <row r="111" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="165"/>
+      <c r="B111" s="155"/>
+      <c r="C111" s="155"/>
+      <c r="D111" s="155"/>
+      <c r="E111" s="155"/>
+    </row>
+    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="155"/>
+      <c r="B112" s="155"/>
+      <c r="C112" s="155"/>
+      <c r="D112" s="155"/>
+      <c r="E112" s="155"/>
+    </row>
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="155"/>
+      <c r="B113" s="155"/>
+      <c r="C113" s="155"/>
+      <c r="D113" s="155"/>
+      <c r="E113" s="155"/>
+    </row>
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="155"/>
+      <c r="B114" s="155"/>
+      <c r="C114" s="155"/>
+      <c r="D114" s="155"/>
+      <c r="E114" s="155"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A83:E85"/>
-    <mergeCell ref="A108:C109"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A68:B69"/>
-    <mergeCell ref="A114:E117"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="A82:E84"/>
+    <mergeCell ref="A105:C106"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A67:B68"/>
+    <mergeCell ref="A111:E114"/>
+    <mergeCell ref="D67:D68"/>
+    <mergeCell ref="E67:E68"/>
     <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="A14:E17"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2878,21 +2846,21 @@
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="6"/>
+      <c r="F1" s="174" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="177" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
-      <c r="K1" s="158"/>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="158"/>
-      <c r="O1" s="158"/>
+      <c r="G1" s="155"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="155"/>
+      <c r="J1" s="155"/>
+      <c r="K1" s="155"/>
+      <c r="L1" s="155"/>
+      <c r="M1" s="155"/>
+      <c r="N1" s="155"/>
+      <c r="O1" s="155"/>
       <c r="P1" s="6"/>
     </row>
     <row r="2" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2911,15 +2879,15 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="182">
+      <c r="O2" s="179">
         <f>T4</f>
         <v>4000000</v>
       </c>
-      <c r="P2" s="158"/>
+      <c r="P2" s="155"/>
       <c r="Q2" s="15"/>
     </row>
     <row r="3" spans="1:20" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2927,7 +2895,7 @@
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
@@ -2937,64 +2905,64 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="186">
+      <c r="O3" s="183">
         <f>S6</f>
         <v>181000</v>
       </c>
-      <c r="P3" s="187"/>
+      <c r="P3" s="184"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="180" t="s">
+      <c r="A4" s="177" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="180" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="183" t="s">
+      <c r="C4" s="170" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="173" t="s">
+      <c r="D4" s="170" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="173" t="s">
+      <c r="E4" s="172" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="175" t="s">
+      <c r="F4" s="170" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="173" t="s">
+      <c r="G4" s="170" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="173" t="s">
+      <c r="H4" s="170" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="173" t="s">
+      <c r="I4" s="172" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="175" t="s">
+      <c r="J4" s="175" t="s">
         <v>72</v>
       </c>
-      <c r="J4" s="178" t="s">
+      <c r="K4" s="178" t="s">
         <v>73</v>
       </c>
-      <c r="K4" s="181" t="s">
+      <c r="L4" s="176" t="s">
         <v>74</v>
       </c>
-      <c r="L4" s="179" t="s">
+      <c r="M4" s="178" t="s">
         <v>75</v>
       </c>
-      <c r="M4" s="181" t="s">
+      <c r="N4" s="178" t="s">
         <v>76</v>
       </c>
-      <c r="N4" s="181" t="s">
+      <c r="O4" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="O4" s="61" t="s">
+      <c r="P4" s="182" t="s">
         <v>78</v>
-      </c>
-      <c r="P4" s="185" t="s">
-        <v>79</v>
       </c>
       <c r="S4" s="43"/>
       <c r="T4">
@@ -3002,54 +2970,54 @@
       </c>
     </row>
     <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="174"/>
-      <c r="B5" s="184"/>
-      <c r="C5" s="174"/>
-      <c r="D5" s="174"/>
-      <c r="E5" s="176"/>
-      <c r="F5" s="174"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="174"/>
-      <c r="I5" s="176"/>
-      <c r="J5" s="176"/>
-      <c r="K5" s="176"/>
-      <c r="L5" s="174"/>
-      <c r="M5" s="176"/>
-      <c r="N5" s="176"/>
+      <c r="A5" s="171"/>
+      <c r="B5" s="181"/>
+      <c r="C5" s="171"/>
+      <c r="D5" s="171"/>
+      <c r="E5" s="173"/>
+      <c r="F5" s="171"/>
+      <c r="G5" s="171"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="173"/>
+      <c r="J5" s="173"/>
+      <c r="K5" s="173"/>
+      <c r="L5" s="171"/>
+      <c r="M5" s="173"/>
+      <c r="N5" s="173"/>
       <c r="O5" s="59" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 15/10</v>
-      </c>
-      <c r="P5" s="174"/>
+        <v>VTO 14/11</v>
+      </c>
+      <c r="P5" s="171"/>
       <c r="T5" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B6" s="62">
         <v>1</v>
       </c>
       <c r="C6" s="62" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="E6" s="62" t="s">
         <v>82</v>
-      </c>
-      <c r="E6" s="62" t="s">
-        <v>83</v>
       </c>
       <c r="F6" s="68">
         <v>3</v>
       </c>
       <c r="G6" s="133">
-        <v>101430.1</v>
+        <v>125430.1</v>
       </c>
       <c r="H6" s="129">
         <f>G6</f>
-        <v>101430.1</v>
+        <v>125430.1</v>
       </c>
       <c r="I6" s="70"/>
       <c r="J6" s="117">
@@ -3090,38 +3058,35 @@
     </row>
     <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B7" s="62">
         <v>2</v>
       </c>
       <c r="C7" s="62" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="D7" s="62" t="s">
+      <c r="E7" s="62" t="s">
         <v>86</v>
-      </c>
-      <c r="E7" s="62" t="s">
-        <v>87</v>
       </c>
       <c r="F7" s="68">
         <v>3.8</v>
       </c>
       <c r="G7" s="133">
-        <v>128478.2</v>
-      </c>
-      <c r="H7" s="129">
-        <f>G7</f>
-        <v>128478.2</v>
-      </c>
+        <v>158878.20000000001</v>
+      </c>
+      <c r="H7" s="129"/>
       <c r="I7" s="70"/>
       <c r="J7" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>158878.20000000001</v>
       </c>
       <c r="K7" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7943.9100000000008</v>
       </c>
       <c r="L7" s="72">
         <f t="shared" si="2"/>
@@ -3133,15 +3098,15 @@
       </c>
       <c r="N7" s="114">
         <f t="shared" si="4"/>
-        <v>158878</v>
+        <v>325700.11</v>
       </c>
       <c r="O7" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$158878,2</v>
+        <v>$325700,2</v>
       </c>
       <c r="P7" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$163644,2</v>
+        <v>$335471,2</v>
       </c>
       <c r="Q7" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3151,37 +3116,37 @@
     </row>
     <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B8" s="62">
         <v>3</v>
       </c>
       <c r="C8" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="62" t="s">
+      <c r="E8" s="62" t="s">
         <v>89</v>
-      </c>
-      <c r="E8" s="62" t="s">
-        <v>90</v>
       </c>
       <c r="F8" s="68">
         <v>3</v>
       </c>
       <c r="G8" s="133">
-        <v>201632.3</v>
+        <v>233936.3</v>
       </c>
       <c r="H8" s="129">
-        <v>98293.3</v>
+        <v>124000</v>
       </c>
       <c r="I8" s="70"/>
       <c r="J8" s="117">
         <f t="shared" si="0"/>
-        <v>103338.99999999999</v>
+        <v>109936.29999999999</v>
       </c>
       <c r="K8" s="71">
         <f t="shared" si="1"/>
-        <v>5166.95</v>
+        <v>5496.8149999999996</v>
       </c>
       <c r="L8" s="72">
         <f t="shared" si="2"/>
@@ -3193,15 +3158,15 @@
       </c>
       <c r="N8" s="114">
         <f t="shared" si="4"/>
-        <v>233935.94999999998</v>
+        <v>240863.11499999999</v>
       </c>
       <c r="O8" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$233936,3</v>
+        <v>$240863,3</v>
       </c>
       <c r="P8" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$240954,3</v>
+        <v>$248089,3</v>
       </c>
       <c r="Q8" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3210,35 +3175,38 @@
     </row>
     <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B9" s="62">
         <v>4</v>
       </c>
       <c r="C9" s="62" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="62" t="s">
         <v>92</v>
       </c>
-      <c r="D9" s="62" t="s">
+      <c r="E9" s="62" t="s">
         <v>93</v>
-      </c>
-      <c r="E9" s="62" t="s">
-        <v>94</v>
       </c>
       <c r="F9" s="68">
         <v>3.1</v>
       </c>
       <c r="G9" s="133">
-        <v>208353.4</v>
-      </c>
-      <c r="H9" s="129"/>
+        <v>348382.4</v>
+      </c>
+      <c r="H9" s="129">
+        <f>10418+208354+129610</f>
+        <v>348382</v>
+      </c>
       <c r="I9" s="70"/>
       <c r="J9" s="117">
         <f t="shared" si="0"/>
-        <v>208353.4</v>
+        <v>0.40000000002328306</v>
       </c>
       <c r="K9" s="71">
         <f t="shared" si="1"/>
-        <v>10417.67</v>
+        <v>2.0000000001164156E-2</v>
       </c>
       <c r="L9" s="72">
         <f t="shared" si="2"/>
@@ -3250,53 +3218,56 @@
       </c>
       <c r="N9" s="114">
         <f t="shared" si="4"/>
-        <v>348382.07</v>
+        <v>129611.42000000003</v>
       </c>
       <c r="O9" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$348382,4</v>
+        <v>$129611,4</v>
       </c>
       <c r="P9" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$358834,4</v>
+        <v>$133500,4</v>
       </c>
       <c r="Q9" s="43" t="str">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="S9" s="43"/>
+      <c r="T9" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B10" s="62">
         <v>5</v>
       </c>
       <c r="C10" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="62" t="s">
         <v>95</v>
       </c>
-      <c r="D10" s="62" t="s">
+      <c r="E10" s="62" t="s">
         <v>96</v>
-      </c>
-      <c r="E10" s="62" t="s">
-        <v>97</v>
       </c>
       <c r="F10" s="68">
         <v>3.1</v>
       </c>
       <c r="G10" s="133">
-        <v>317072.5</v>
+        <v>462537.5</v>
       </c>
       <c r="H10" s="129"/>
       <c r="I10" s="70"/>
       <c r="J10" s="117">
         <f t="shared" si="0"/>
-        <v>317072.5</v>
+        <v>462537.5</v>
       </c>
       <c r="K10" s="71">
         <f t="shared" si="1"/>
-        <v>15853.625</v>
+        <v>23126.875</v>
       </c>
       <c r="L10" s="72">
         <f t="shared" si="2"/>
@@ -3308,15 +3279,15 @@
       </c>
       <c r="N10" s="114">
         <f t="shared" si="4"/>
-        <v>462537.125</v>
+        <v>615275.375</v>
       </c>
       <c r="O10" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$462537,5</v>
+        <v>$615275,5</v>
       </c>
       <c r="P10" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$476413,5</v>
+        <v>$633734,5</v>
       </c>
       <c r="Q10" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3326,27 +3297,27 @@
     </row>
     <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B11" s="62">
         <v>6</v>
       </c>
       <c r="C11" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="62" t="s">
         <v>99</v>
-      </c>
-      <c r="D11" s="62" t="s">
-        <v>100</v>
       </c>
       <c r="E11" s="62"/>
       <c r="F11" s="68">
         <v>3.2</v>
       </c>
       <c r="G11" s="133">
-        <v>108192.6</v>
+        <v>133792.6</v>
       </c>
       <c r="H11" s="129">
         <f>G11</f>
-        <v>108192.6</v>
+        <v>133792.6</v>
       </c>
       <c r="I11" s="70"/>
       <c r="J11" s="117">
@@ -3384,29 +3355,29 @@
     </row>
     <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B12" s="62">
         <v>7</v>
       </c>
       <c r="C12" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="62" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="62" t="s">
+      <c r="E12" s="62" t="s">
         <v>102</v>
-      </c>
-      <c r="E12" s="62" t="s">
-        <v>103</v>
       </c>
       <c r="F12" s="68">
         <v>3.3</v>
       </c>
       <c r="G12" s="133">
-        <v>111573.7</v>
+        <v>137973.70000000001</v>
       </c>
       <c r="H12" s="129">
         <f>G12</f>
-        <v>111573.7</v>
+        <v>137973.70000000001</v>
       </c>
       <c r="I12" s="70"/>
       <c r="J12" s="117">
@@ -3444,38 +3415,37 @@
     </row>
     <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B13" s="62">
         <v>23</v>
       </c>
       <c r="C13" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="D13" s="62" t="s">
+      <c r="E13" s="62" t="s">
         <v>106</v>
-      </c>
-      <c r="E13" s="62" t="s">
-        <v>107</v>
       </c>
       <c r="F13" s="68">
         <v>6.3</v>
       </c>
       <c r="G13" s="133">
-        <v>212403.23</v>
+        <v>262803.23</v>
       </c>
       <c r="H13" s="69">
-        <f>201600+11403</f>
-        <v>213003</v>
+        <v>252000</v>
       </c>
       <c r="I13" s="70"/>
       <c r="J13" s="117">
         <f t="shared" si="0"/>
-        <v>-599.76999999998952</v>
+        <v>10803.229999999981</v>
       </c>
       <c r="K13" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>540.16149999999914</v>
       </c>
       <c r="L13" s="72">
         <f t="shared" si="2"/>
@@ -3487,58 +3457,57 @@
       </c>
       <c r="N13" s="114">
         <f t="shared" si="4"/>
-        <v>262803.23</v>
+        <v>274746.39149999997</v>
       </c>
       <c r="O13" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$262803,23</v>
+        <v>$274746,23</v>
       </c>
       <c r="P13" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$270687,23</v>
+        <v>$282989,23</v>
       </c>
       <c r="Q13" s="43" t="str">
         <f t="shared" si="7"/>
         <v>23</v>
       </c>
       <c r="S13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B14" s="62">
         <v>22</v>
       </c>
       <c r="C14" s="62" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="62" t="s">
+      <c r="E14" s="62" t="s">
         <v>110</v>
-      </c>
-      <c r="E14" s="62" t="s">
-        <v>111</v>
       </c>
       <c r="F14" s="68">
         <v>5.0999999999999996</v>
       </c>
       <c r="G14" s="133">
-        <v>172431.22</v>
+        <v>2196288.2200000002</v>
       </c>
       <c r="H14" s="69">
-        <f>G14</f>
-        <v>172431.22</v>
+        <v>213231.22</v>
       </c>
       <c r="I14" s="70"/>
       <c r="J14" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1983057.0000000002</v>
       </c>
       <c r="K14" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>99152.85000000002</v>
       </c>
       <c r="L14" s="72">
         <f t="shared" si="2"/>
@@ -3550,15 +3519,15 @@
       </c>
       <c r="N14" s="114">
         <f t="shared" si="4"/>
-        <v>213231</v>
+        <v>2295440.8500000006</v>
       </c>
       <c r="O14" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$213231,22</v>
+        <v>$2295441,22</v>
       </c>
       <c r="P14" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$219628,22</v>
+        <v>$2364304,22</v>
       </c>
       <c r="Q14" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3567,27 +3536,27 @@
     </row>
     <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B15" s="62">
         <v>21</v>
       </c>
       <c r="C15" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" s="62" t="s">
         <v>113</v>
-      </c>
-      <c r="D15" s="62" t="s">
-        <v>114</v>
       </c>
       <c r="E15" s="63"/>
       <c r="F15" s="68">
         <v>8.1999999999999993</v>
       </c>
       <c r="G15" s="133">
-        <v>269417.21000000002</v>
+        <v>342842.21</v>
       </c>
       <c r="H15" s="69">
         <f>G15</f>
-        <v>269417.21000000002</v>
+        <v>342842.21</v>
       </c>
       <c r="I15" s="70"/>
       <c r="J15" s="117">
@@ -3625,29 +3594,29 @@
     </row>
     <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B16" s="62">
         <v>14</v>
       </c>
       <c r="C16" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" s="62" t="s">
         <v>115</v>
       </c>
-      <c r="D16" s="62" t="s">
+      <c r="E16" s="62" t="s">
         <v>116</v>
-      </c>
-      <c r="E16" s="62" t="s">
-        <v>117</v>
       </c>
       <c r="F16" s="68">
         <v>6.1</v>
       </c>
       <c r="G16" s="133">
-        <v>206241.14</v>
+        <v>255041.14</v>
       </c>
       <c r="H16" s="69">
         <f>G16</f>
-        <v>206241.14</v>
+        <v>255041.14</v>
       </c>
       <c r="I16" s="70"/>
       <c r="J16" s="117">
@@ -3685,32 +3654,31 @@
     </row>
     <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B17" s="62">
         <v>13</v>
       </c>
       <c r="C17" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="62" t="s">
         <v>119</v>
-      </c>
-      <c r="D17" s="62" t="s">
-        <v>120</v>
       </c>
       <c r="E17" s="63"/>
       <c r="F17" s="68">
         <v>5</v>
       </c>
       <c r="G17" s="133">
-        <v>169351.13</v>
+        <v>209050.13</v>
       </c>
       <c r="H17" s="69">
-        <f>G17</f>
-        <v>169351.13</v>
+        <v>215322.13</v>
       </c>
       <c r="I17" s="70"/>
       <c r="J17" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-6272</v>
       </c>
       <c r="K17" s="71">
         <f t="shared" si="1"/>
@@ -3726,15 +3694,15 @@
       </c>
       <c r="N17" s="114">
         <f t="shared" si="4"/>
-        <v>209050</v>
+        <v>202778</v>
       </c>
       <c r="O17" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$209050,13</v>
+        <v>$202778,13</v>
       </c>
       <c r="P17" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$215322,13</v>
+        <v>$208861,13</v>
       </c>
       <c r="Q17" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3743,37 +3711,37 @@
     </row>
     <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B18" s="62">
         <v>12</v>
       </c>
       <c r="C18" s="62" t="s">
+        <v>120</v>
+      </c>
+      <c r="D18" s="62" t="s">
         <v>121</v>
       </c>
-      <c r="D18" s="62" t="s">
+      <c r="E18" s="62" t="s">
         <v>122</v>
-      </c>
-      <c r="E18" s="62" t="s">
-        <v>123</v>
       </c>
       <c r="F18" s="68">
         <v>8.1999999999999993</v>
       </c>
       <c r="G18" s="133">
-        <v>15822586.119999999</v>
+        <v>16665453.119999999</v>
       </c>
       <c r="H18" s="69">
-        <v>277242</v>
+        <v>342842</v>
       </c>
       <c r="I18" s="70"/>
       <c r="J18" s="117">
         <f t="shared" si="0"/>
-        <v>15545344.119999999</v>
+        <v>16322611.119999999</v>
       </c>
       <c r="K18" s="71">
         <f t="shared" si="1"/>
-        <v>777267.20600000001</v>
+        <v>816130.55599999998</v>
       </c>
       <c r="L18" s="72">
         <f t="shared" si="2"/>
@@ -3785,15 +3753,15 @@
       </c>
       <c r="N18" s="114">
         <f t="shared" si="4"/>
-        <v>16665453.325999999</v>
+        <v>17481583.675999999</v>
       </c>
       <c r="O18" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$16665453,12</v>
+        <v>$17481584,12</v>
       </c>
       <c r="P18" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$17165417,12</v>
+        <v>$18006031,12</v>
       </c>
       <c r="Q18" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3802,33 +3770,33 @@
     </row>
     <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B19" s="62">
         <v>17</v>
       </c>
       <c r="C19" s="62" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D19" s="62" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E19" s="63"/>
       <c r="F19" s="68">
         <v>6.1</v>
       </c>
       <c r="G19" s="133">
-        <v>11648915.17</v>
+        <v>12486402.17</v>
       </c>
       <c r="H19" s="69"/>
       <c r="I19" s="70"/>
       <c r="J19" s="117">
         <f t="shared" si="0"/>
-        <v>11648915.17</v>
+        <v>12486402.17</v>
       </c>
       <c r="K19" s="71">
         <f t="shared" si="1"/>
-        <v>582445.7585</v>
+        <v>624320.10849999997</v>
       </c>
       <c r="L19" s="72">
         <f t="shared" si="2"/>
@@ -3840,15 +3808,15 @@
       </c>
       <c r="N19" s="114">
         <f t="shared" si="4"/>
-        <v>12486401.9285</v>
+        <v>13365763.2785</v>
       </c>
       <c r="O19" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$12486402,17</v>
+        <v>$13365763,17</v>
       </c>
       <c r="P19" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$12860994,17</v>
+        <v>$13766736,17</v>
       </c>
       <c r="Q19" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3857,33 +3825,34 @@
     </row>
     <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B20" s="62">
         <v>16</v>
       </c>
       <c r="C20" s="62" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="62" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="62" t="s">
+      <c r="E20" s="63" t="s">
         <v>127</v>
-      </c>
-      <c r="E20" s="63" t="s">
-        <v>128</v>
       </c>
       <c r="F20" s="68">
         <v>5</v>
       </c>
       <c r="G20" s="134">
-        <v>173143.16</v>
+        <v>214439.16</v>
       </c>
       <c r="H20" s="129">
-        <v>174000</v>
+        <f>134000+81000</f>
+        <v>215000</v>
       </c>
       <c r="I20" s="70"/>
       <c r="J20" s="117">
         <f t="shared" si="0"/>
-        <v>-856.83999999999651</v>
+        <v>-560.83999999999651</v>
       </c>
       <c r="K20" s="71">
         <f t="shared" si="1"/>
@@ -3899,47 +3868,47 @@
       </c>
       <c r="N20" s="114">
         <f t="shared" si="4"/>
-        <v>208193.16</v>
+        <v>208489.16</v>
       </c>
       <c r="O20" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$208193,16</v>
+        <v>$208489,16</v>
       </c>
       <c r="P20" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$214439,16</v>
+        <v>$214744,16</v>
       </c>
       <c r="Q20" s="43" t="str">
         <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="S20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B21" s="62">
         <v>15</v>
       </c>
       <c r="C21" s="62" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" s="62" t="s">
         <v>130</v>
-      </c>
-      <c r="D21" s="62" t="s">
-        <v>131</v>
       </c>
       <c r="E21" s="62"/>
       <c r="F21" s="68">
         <v>8.1999999999999993</v>
       </c>
       <c r="G21" s="133">
-        <v>273166.15000000002</v>
+        <v>342842.15</v>
       </c>
       <c r="H21" s="69">
         <f>G21</f>
-        <v>273166.15000000002</v>
+        <v>342842.15</v>
       </c>
       <c r="I21" s="70"/>
       <c r="J21" s="117">
@@ -3978,33 +3947,36 @@
     </row>
     <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B22" s="62">
         <v>20</v>
       </c>
       <c r="C22" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="D22" s="62" t="s">
         <v>132</v>
-      </c>
-      <c r="D22" s="62" t="s">
-        <v>133</v>
       </c>
       <c r="E22" s="63"/>
       <c r="F22" s="68">
         <v>6.1</v>
       </c>
       <c r="G22" s="134">
-        <v>206241.2</v>
-      </c>
-      <c r="H22" s="69"/>
+        <v>471594.2</v>
+      </c>
+      <c r="H22" s="69">
+        <f>G22</f>
+        <v>471594.2</v>
+      </c>
       <c r="I22" s="70"/>
       <c r="J22" s="71">
         <f t="shared" si="0"/>
-        <v>206241.2</v>
+        <v>0</v>
       </c>
       <c r="K22" s="71">
         <f t="shared" si="1"/>
-        <v>10312.060000000001</v>
+        <v>0</v>
       </c>
       <c r="L22" s="72">
         <f t="shared" si="2"/>
@@ -4016,57 +3988,58 @@
       </c>
       <c r="N22" s="114">
         <f t="shared" si="4"/>
-        <v>471594.26</v>
+        <v>255041</v>
       </c>
       <c r="O22" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$471594,20</v>
+        <v>$255041,20</v>
       </c>
       <c r="P22" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$485742,20</v>
+        <v>$262692,20</v>
       </c>
       <c r="Q22" s="43" t="str">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="T22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B23" s="62">
         <v>19</v>
       </c>
       <c r="C23" s="62" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="62" t="s">
         <v>136</v>
       </c>
-      <c r="D23" s="62" t="s">
-        <v>137</v>
-      </c>
       <c r="E23" s="62" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F23" s="68">
         <v>5</v>
       </c>
       <c r="G23" s="133">
-        <v>169050.19</v>
+        <v>218553.19</v>
       </c>
       <c r="H23" s="69">
-        <v>160000</v>
+        <f>G23</f>
+        <v>218553.19</v>
       </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71">
         <f t="shared" si="0"/>
-        <v>9050.1900000000023</v>
+        <v>0</v>
       </c>
       <c r="K23" s="71">
         <f t="shared" si="1"/>
-        <v>452.50950000000012</v>
+        <v>0</v>
       </c>
       <c r="L23" s="72">
         <f t="shared" si="2"/>
@@ -4078,56 +4051,56 @@
       </c>
       <c r="N23" s="114">
         <f t="shared" si="4"/>
-        <v>218552.69949999999</v>
+        <v>209050</v>
       </c>
       <c r="O23" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$218553,19</v>
+        <v>$209050,19</v>
       </c>
       <c r="P23" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$225109,19</v>
+        <v>$215322,19</v>
       </c>
       <c r="Q23" s="43" t="str">
         <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="S23" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B24" s="62">
         <v>18</v>
       </c>
       <c r="C24" s="62" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" s="151" t="s">
         <v>138</v>
-      </c>
-      <c r="D24" s="151" t="s">
-        <v>139</v>
       </c>
       <c r="E24" s="63"/>
       <c r="F24" s="68">
         <v>8.1999999999999993</v>
       </c>
       <c r="G24" s="133">
-        <v>268259.18</v>
+        <v>343824.18</v>
       </c>
       <c r="H24" s="69">
-        <f>267324.18</f>
-        <v>267324.18</v>
+        <f>G24</f>
+        <v>343824.18</v>
       </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71">
         <f t="shared" si="0"/>
-        <v>935</v>
+        <v>0</v>
       </c>
       <c r="K24" s="71">
         <f t="shared" si="1"/>
-        <v>46.75</v>
+        <v>0</v>
       </c>
       <c r="L24" s="72">
         <f t="shared" si="2"/>
@@ -4139,22 +4112,22 @@
       </c>
       <c r="N24" s="114">
         <f t="shared" si="4"/>
-        <v>343823.74999999994</v>
+        <v>342841.99999999994</v>
       </c>
       <c r="O24" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$343824,18</v>
+        <v>$342842,18</v>
       </c>
       <c r="P24" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$354138,18</v>
+        <v>$353127,18</v>
       </c>
       <c r="Q24" s="43" t="str">
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="T24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4168,11 +4141,11 @@
       </c>
       <c r="G25" s="54">
         <f t="shared" si="8"/>
-        <v>30767937.899999995</v>
+        <v>35610063.899999991</v>
       </c>
       <c r="H25" s="60">
         <f t="shared" si="8"/>
-        <v>2730143.9299999997</v>
+        <v>4082670.82</v>
       </c>
       <c r="I25" s="54">
         <f t="shared" si="8"/>
@@ -4180,11 +4153,11 @@
       </c>
       <c r="J25" s="60">
         <f t="shared" si="8"/>
-        <v>28037793.970000003</v>
+        <v>31527393.080000002</v>
       </c>
       <c r="K25" s="60">
         <f t="shared" si="8"/>
-        <v>1401962.5289999999</v>
+        <v>1576711.2960000001</v>
       </c>
       <c r="L25" s="60">
         <f t="shared" si="8"/>
@@ -4211,90 +4184,90 @@
     </row>
     <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="168" t="s">
-        <v>141</v>
-      </c>
-      <c r="E28" s="158"/>
-      <c r="F28" s="158"/>
-      <c r="G28" s="158"/>
-      <c r="H28" s="158"/>
-      <c r="I28" s="158"/>
-      <c r="J28" s="158"/>
-      <c r="K28" s="158"/>
-      <c r="L28" s="158"/>
-      <c r="M28" s="158"/>
-      <c r="N28" s="158"/>
-      <c r="O28" s="158"/>
+      <c r="D28" s="165" t="s">
+        <v>140</v>
+      </c>
+      <c r="E28" s="155"/>
+      <c r="F28" s="155"/>
+      <c r="G28" s="155"/>
+      <c r="H28" s="155"/>
+      <c r="I28" s="155"/>
+      <c r="J28" s="155"/>
+      <c r="K28" s="155"/>
+      <c r="L28" s="155"/>
+      <c r="M28" s="155"/>
+      <c r="N28" s="155"/>
+      <c r="O28" s="155"/>
     </row>
     <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D29" s="158"/>
-      <c r="E29" s="158"/>
-      <c r="F29" s="158"/>
-      <c r="G29" s="158"/>
-      <c r="H29" s="158"/>
-      <c r="I29" s="158"/>
-      <c r="J29" s="158"/>
-      <c r="K29" s="158"/>
-      <c r="L29" s="158"/>
-      <c r="M29" s="158"/>
-      <c r="N29" s="158"/>
-      <c r="O29" s="158"/>
+      <c r="D29" s="155"/>
+      <c r="E29" s="155"/>
+      <c r="F29" s="155"/>
+      <c r="G29" s="155"/>
+      <c r="H29" s="155"/>
+      <c r="I29" s="155"/>
+      <c r="J29" s="155"/>
+      <c r="K29" s="155"/>
+      <c r="L29" s="155"/>
+      <c r="M29" s="155"/>
+      <c r="N29" s="155"/>
+      <c r="O29" s="155"/>
     </row>
     <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="158"/>
-      <c r="E30" s="158"/>
-      <c r="F30" s="158"/>
-      <c r="G30" s="158"/>
-      <c r="H30" s="158"/>
-      <c r="I30" s="158"/>
-      <c r="J30" s="158"/>
-      <c r="K30" s="158"/>
-      <c r="L30" s="158"/>
-      <c r="M30" s="158"/>
-      <c r="N30" s="158"/>
-      <c r="O30" s="158"/>
+      <c r="D30" s="155"/>
+      <c r="E30" s="155"/>
+      <c r="F30" s="155"/>
+      <c r="G30" s="155"/>
+      <c r="H30" s="155"/>
+      <c r="I30" s="155"/>
+      <c r="J30" s="155"/>
+      <c r="K30" s="155"/>
+      <c r="L30" s="155"/>
+      <c r="M30" s="155"/>
+      <c r="N30" s="155"/>
+      <c r="O30" s="155"/>
     </row>
     <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="158"/>
-      <c r="E31" s="158"/>
-      <c r="F31" s="158"/>
-      <c r="G31" s="158"/>
-      <c r="H31" s="158"/>
-      <c r="I31" s="158"/>
-      <c r="J31" s="158"/>
-      <c r="K31" s="158"/>
-      <c r="L31" s="158"/>
-      <c r="M31" s="158"/>
-      <c r="N31" s="158"/>
-      <c r="O31" s="158"/>
+      <c r="D31" s="155"/>
+      <c r="E31" s="155"/>
+      <c r="F31" s="155"/>
+      <c r="G31" s="155"/>
+      <c r="H31" s="155"/>
+      <c r="I31" s="155"/>
+      <c r="J31" s="155"/>
+      <c r="K31" s="155"/>
+      <c r="L31" s="155"/>
+      <c r="M31" s="155"/>
+      <c r="N31" s="155"/>
+      <c r="O31" s="155"/>
     </row>
     <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D32" s="158"/>
-      <c r="E32" s="158"/>
-      <c r="F32" s="158"/>
-      <c r="G32" s="158"/>
-      <c r="H32" s="158"/>
-      <c r="I32" s="158"/>
-      <c r="J32" s="158"/>
-      <c r="K32" s="158"/>
-      <c r="L32" s="158"/>
-      <c r="M32" s="158"/>
-      <c r="N32" s="158"/>
-      <c r="O32" s="158"/>
+      <c r="D32" s="155"/>
+      <c r="E32" s="155"/>
+      <c r="F32" s="155"/>
+      <c r="G32" s="155"/>
+      <c r="H32" s="155"/>
+      <c r="I32" s="155"/>
+      <c r="J32" s="155"/>
+      <c r="K32" s="155"/>
+      <c r="L32" s="155"/>
+      <c r="M32" s="155"/>
+      <c r="N32" s="155"/>
+      <c r="O32" s="155"/>
     </row>
     <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="158"/>
-      <c r="E33" s="158"/>
-      <c r="F33" s="158"/>
-      <c r="G33" s="158"/>
-      <c r="H33" s="158"/>
-      <c r="I33" s="158"/>
-      <c r="J33" s="158"/>
-      <c r="K33" s="158"/>
-      <c r="L33" s="158"/>
-      <c r="M33" s="158"/>
-      <c r="N33" s="158"/>
-      <c r="O33" s="158"/>
+      <c r="D33" s="155"/>
+      <c r="E33" s="155"/>
+      <c r="F33" s="155"/>
+      <c r="G33" s="155"/>
+      <c r="H33" s="155"/>
+      <c r="I33" s="155"/>
+      <c r="J33" s="155"/>
+      <c r="K33" s="155"/>
+      <c r="L33" s="155"/>
+      <c r="M33" s="155"/>
+      <c r="N33" s="155"/>
+      <c r="O33" s="155"/>
       <c r="R33" s="104"/>
       <c r="S33" s="104"/>
       <c r="T33" s="104"/>

--- a/PUEYRREDON 1494/Octubre/PUEYRREDON Octubre.xlsx
+++ b/PUEYRREDON 1494/Octubre/PUEYRREDON Octubre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PUEYRREDON 1494\Octubre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PUEYRREDON 1494\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E7D1BA-CD67-497B-B5CB-B906105CCE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF48B94B-02C0-46A4-8527-EFD7AC356B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="162">
   <si>
     <t>MAIL: consorciopueyrredon1494@gmail.com</t>
   </si>
@@ -508,6 +508,9 @@
   </si>
   <si>
     <t>PAULA</t>
+  </si>
+  <si>
+    <t>REVISAR QUE HUBO UN PROBLEMA CON EL 1B, EL MES PASADO LO HABIAMOS PUESTO CON UNA DEUDA ENORME CUANDO NO ERA CORRECTA</t>
   </si>
 </sst>
 </file>
@@ -1190,7 +1193,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1397,26 +1400,18 @@
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
@@ -1431,26 +1426,26 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1468,7 +1463,31 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="9" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="23" fillId="9" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="23" fillId="9" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1825,27 +1844,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M114"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="140"/>
       <c r="B1" s="141"/>
       <c r="C1" s="142"/>
       <c r="D1" s="142"/>
       <c r="E1" s="143"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="144"/>
       <c r="B2" s="136" t="s">
         <v>0</v>
@@ -1854,7 +1873,7 @@
       <c r="D2" s="136"/>
       <c r="E2" s="145"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="144"/>
       <c r="B3" s="136" t="s">
         <v>1</v>
@@ -1863,7 +1882,7 @@
       <c r="D3" s="136"/>
       <c r="E3" s="145"/>
     </row>
-    <row r="4" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="144"/>
       <c r="B4" s="137" t="s">
         <v>2</v>
@@ -1874,7 +1893,7 @@
       </c>
       <c r="E4" s="145"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="144" t="s">
         <v>4</v>
       </c>
@@ -1885,7 +1904,7 @@
       <c r="D5" s="135"/>
       <c r="E5" s="146"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="144" t="s">
         <v>6</v>
       </c>
@@ -1898,7 +1917,7 @@
       </c>
       <c r="E6" s="146"/>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="147" t="s">
         <v>8</v>
       </c>
@@ -1907,60 +1926,60 @@
       <c r="D7" s="148"/>
       <c r="E7" s="149"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="154" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="168" t="s">
         <v>147</v>
       </c>
-      <c r="C9" s="155"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="155"/>
-      <c r="C10" s="155"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="155"/>
-      <c r="C11" s="155"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C9" s="156"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="156"/>
+      <c r="C10" s="156"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="156"/>
+      <c r="C11" s="156"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" s="132"/>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="158" t="s">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="155"/>
-      <c r="C14" s="155"/>
-      <c r="D14" s="155"/>
-      <c r="E14" s="155"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="155"/>
-      <c r="B15" s="155"/>
-      <c r="C15" s="155"/>
-      <c r="D15" s="155"/>
-      <c r="E15" s="155"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="155"/>
-      <c r="B16" s="155"/>
-      <c r="C16" s="155"/>
-      <c r="D16" s="155"/>
-      <c r="E16" s="155"/>
-    </row>
-    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="155"/>
-      <c r="B17" s="155"/>
-      <c r="C17" s="155"/>
-      <c r="D17" s="155"/>
-      <c r="E17" s="155"/>
-    </row>
-    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="156"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="156"/>
+      <c r="B15" s="156"/>
+      <c r="C15" s="156"/>
+      <c r="D15" s="156"/>
+      <c r="E15" s="156"/>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="156"/>
+      <c r="B16" s="156"/>
+      <c r="C16" s="156"/>
+      <c r="D16" s="156"/>
+      <c r="E16" s="156"/>
+    </row>
+    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="156"/>
+      <c r="B17" s="156"/>
+      <c r="C17" s="156"/>
+      <c r="D17" s="156"/>
+      <c r="E17" s="156"/>
+    </row>
+    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>10</v>
       </c>
@@ -1969,7 +1988,7 @@
       <c r="D21" s="9"/>
       <c r="E21" s="14"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="32" t="s">
         <v>11</v>
       </c>
@@ -1978,7 +1997,7 @@
       <c r="D22" s="30"/>
       <c r="E22" s="30"/>
     </row>
-    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>12</v>
       </c>
@@ -1989,7 +2008,7 @@
       </c>
       <c r="E23" s="80"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>13</v>
       </c>
@@ -2000,7 +2019,7 @@
       </c>
       <c r="E24" s="80"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>14</v>
       </c>
@@ -2010,7 +2029,7 @@
       <c r="E25" s="80"/>
       <c r="H25" s="15"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2018,7 +2037,7 @@
       <c r="E26" s="80"/>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="57" t="s">
         <v>15</v>
       </c>
@@ -2031,7 +2050,7 @@
       <c r="E27" s="81"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:8" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2039,7 +2058,7 @@
       <c r="E28" s="80"/>
       <c r="H28" s="15"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2047,7 +2066,7 @@
       <c r="E29" s="80"/>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="57" t="s">
         <v>15</v>
       </c>
@@ -2059,7 +2078,7 @@
       </c>
       <c r="E30" s="81"/>
     </row>
-    <row r="31" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="23" t="s">
         <v>16</v>
       </c>
@@ -2072,7 +2091,7 @@
       </c>
       <c r="F31" s="15"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="32" t="s">
         <v>17</v>
       </c>
@@ -2081,7 +2100,7 @@
       <c r="D32" s="123"/>
       <c r="E32" s="83"/>
     </row>
-    <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="64" t="s">
         <v>18</v>
       </c>
@@ -2094,7 +2113,7 @@
       </c>
       <c r="E33" s="84"/>
     </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>19</v>
       </c>
@@ -2110,7 +2129,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="23" t="s">
         <v>20</v>
       </c>
@@ -2122,7 +2141,7 @@
         <v>182100</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="30" t="s">
         <v>21</v>
       </c>
@@ -2131,29 +2150,29 @@
       <c r="D36" s="125"/>
       <c r="E36" s="66"/>
     </row>
-    <row r="37" spans="1:8" s="36" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="159" t="s">
+    <row r="37" spans="1:8" s="36" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="170" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="157"/>
+      <c r="B37" s="159"/>
       <c r="C37" s="55"/>
       <c r="D37" s="153">
         <v>87562.7</v>
       </c>
       <c r="E37" s="106"/>
     </row>
-    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="159" t="s">
+    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="170" t="s">
         <v>23</v>
       </c>
-      <c r="B38" s="157"/>
+      <c r="B38" s="159"/>
       <c r="C38" s="55"/>
       <c r="D38" s="126">
         <v>6646.91</v>
       </c>
       <c r="E38" s="106"/>
     </row>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="23" t="s">
         <v>24</v>
       </c>
@@ -2165,7 +2184,7 @@
         <v>94209.61</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="32" t="s">
         <v>25</v>
       </c>
@@ -2174,7 +2193,7 @@
       <c r="D40" s="127"/>
       <c r="E40" s="87"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>26</v>
       </c>
@@ -2188,7 +2207,7 @@
       </c>
       <c r="G41" s="104"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>150</v>
       </c>
@@ -2203,7 +2222,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="str">
         <f>A42</f>
         <v>Sindicatos mes de OCTUBRE</v>
@@ -2220,7 +2239,7 @@
         <v>Debito 14/10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de OCTUBRE</v>
@@ -2237,7 +2256,7 @@
         <v>Debito 14/10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="23" t="s">
         <v>30</v>
       </c>
@@ -2249,7 +2268,7 @@
         <v>513361.68000000005</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="32" t="s">
         <v>31</v>
       </c>
@@ -2258,7 +2277,7 @@
       <c r="D46" s="127"/>
       <c r="E46" s="87"/>
     </row>
-    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="53" t="s">
         <v>151</v>
       </c>
@@ -2272,7 +2291,7 @@
       </c>
       <c r="G47" s="112"/>
     </row>
-    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>32</v>
       </c>
@@ -2286,7 +2305,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>33</v>
       </c>
@@ -2299,7 +2318,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>141</v>
       </c>
@@ -2312,20 +2331,20 @@
         <v>155</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="156" t="s">
+    <row r="51" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="158" t="s">
         <v>157</v>
       </c>
-      <c r="B51" s="157"/>
+      <c r="B51" s="159"/>
       <c r="C51" s="56"/>
-      <c r="D51" s="185">
+      <c r="D51" s="154">
         <v>640000</v>
       </c>
       <c r="E51" s="90" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="23" t="s">
         <v>34</v>
       </c>
@@ -2337,7 +2356,7 @@
         <v>841810.09</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="32" t="s">
         <v>35</v>
       </c>
@@ -2346,14 +2365,14 @@
       <c r="D53" s="124"/>
       <c r="E53" s="89"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="53"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="34"/>
       <c r="E54" s="88"/>
     </row>
-    <row r="55" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="23" t="s">
         <v>36</v>
       </c>
@@ -2365,7 +2384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="32" t="s">
         <v>37</v>
       </c>
@@ -2374,7 +2393,7 @@
       <c r="D56" s="122"/>
       <c r="E56" s="89"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>37</v>
       </c>
@@ -2385,7 +2404,7 @@
       </c>
       <c r="E57" s="93"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>38</v>
       </c>
@@ -2396,7 +2415,7 @@
       </c>
       <c r="E58" s="91"/>
     </row>
-    <row r="59" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="52" t="s">
         <v>20</v>
       </c>
@@ -2408,14 +2427,14 @@
         <v>103641.06</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="80"/>
       <c r="E60" s="95"/>
     </row>
-    <row r="61" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="25" t="s">
         <v>39</v>
       </c>
@@ -2427,13 +2446,13 @@
         <v>1572455.1300000001</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
       <c r="D62" s="98"/>
       <c r="E62" s="99"/>
       <c r="F62" s="43"/>
     </row>
-    <row r="63" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>40</v>
       </c>
@@ -2447,16 +2466,16 @@
       <c r="F63" s="43"/>
       <c r="G63" s="112"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D64" s="98"/>
       <c r="E64" s="98"/>
       <c r="G64" s="112"/>
     </row>
-    <row r="65" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D65" s="98"/>
       <c r="E65" s="98"/>
     </row>
-    <row r="66" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="11" t="s">
         <v>41</v>
       </c>
@@ -2465,32 +2484,32 @@
       <c r="D66" s="102"/>
       <c r="E66" s="103"/>
     </row>
-    <row r="67" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="156" t="s">
+    <row r="67" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="158" t="s">
         <v>159</v>
       </c>
-      <c r="B67" s="162"/>
+      <c r="B67" s="160"/>
       <c r="C67" s="5"/>
-      <c r="D67" s="166">
+      <c r="D67" s="164">
         <v>181000</v>
       </c>
-      <c r="E67" s="168"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="163"/>
-      <c r="B68" s="164"/>
+      <c r="E67" s="166"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="161"/>
+      <c r="B68" s="162"/>
       <c r="C68" s="53"/>
-      <c r="D68" s="167"/>
-      <c r="E68" s="169"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="156"/>
-      <c r="B69" s="157"/>
+      <c r="D68" s="165"/>
+      <c r="E68" s="167"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="158"/>
+      <c r="B69" s="159"/>
       <c r="C69" s="53"/>
       <c r="D69" s="34"/>
       <c r="E69" s="130"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="50"/>
       <c r="B70" s="49"/>
       <c r="C70" s="49"/>
@@ -2500,7 +2519,7 @@
         <v>181000</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="25" t="s">
         <v>42</v>
       </c>
@@ -2509,8 +2528,8 @@
       <c r="D72" s="26"/>
       <c r="E72" s="113"/>
     </row>
-    <row r="73" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="74" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="74" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>43</v>
       </c>
@@ -2522,8 +2541,8 @@
         <v>181000</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="78" t="s">
         <v>44</v>
       </c>
@@ -2533,7 +2552,7 @@
       </c>
       <c r="D76" s="43"/>
     </row>
-    <row r="77" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="78" t="s">
         <v>45</v>
       </c>
@@ -2542,7 +2561,7 @@
         <v>2427544.87</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="78" t="s">
         <v>46</v>
       </c>
@@ -2551,7 +2570,7 @@
         <v>181000</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="78" t="s">
         <v>47</v>
       </c>
@@ -2560,37 +2579,37 @@
         <v>181000</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="160"/>
-      <c r="B82" s="155"/>
-      <c r="C82" s="155"/>
-      <c r="D82" s="155"/>
-      <c r="E82" s="155"/>
-    </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="155"/>
-      <c r="B83" s="155"/>
-      <c r="C83" s="155"/>
-      <c r="D83" s="155"/>
-      <c r="E83" s="155"/>
-    </row>
-    <row r="84" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="155"/>
-      <c r="B84" s="155"/>
-      <c r="C84" s="155"/>
-      <c r="D84" s="155"/>
-      <c r="E84" s="155"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="155"/>
+      <c r="B82" s="156"/>
+      <c r="C82" s="156"/>
+      <c r="D82" s="156"/>
+      <c r="E82" s="156"/>
+    </row>
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="156"/>
+      <c r="B83" s="156"/>
+      <c r="C83" s="156"/>
+      <c r="D83" s="156"/>
+      <c r="E83" s="156"/>
+    </row>
+    <row r="84" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="156"/>
+      <c r="B84" s="156"/>
+      <c r="C84" s="156"/>
+      <c r="D84" s="156"/>
+      <c r="E84" s="156"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="16" t="s">
         <v>48</v>
       </c>
       <c r="B86" s="38"/>
       <c r="C86" s="17"/>
     </row>
-    <row r="87" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="28" t="s">
         <v>49</v>
       </c>
@@ -2599,17 +2618,17 @@
       </c>
       <c r="C87" s="19"/>
     </row>
-    <row r="88" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="18" t="s">
         <v>50</v>
       </c>
       <c r="B88" s="39">
         <f>PRORRATEO!H25</f>
-        <v>4082670.82</v>
+        <v>4084439.6</v>
       </c>
       <c r="C88" s="17"/>
     </row>
-    <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="150" t="s">
         <v>143</v>
       </c>
@@ -2619,7 +2638,7 @@
       </c>
       <c r="C89" s="17"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="18" t="s">
         <v>51</v>
       </c>
@@ -2629,7 +2648,7 @@
       </c>
       <c r="C90" s="17"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="37" t="s">
         <v>52</v>
       </c>
@@ -2639,7 +2658,7 @@
       </c>
       <c r="C91" s="17"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="21" t="s">
         <v>53</v>
       </c>
@@ -2649,30 +2668,30 @@
       </c>
       <c r="C92" s="17"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="27" t="s">
         <v>36</v>
       </c>
       <c r="B93" s="110">
         <f>SUM(B87:B92)</f>
-        <v>1663367.1524999999</v>
+        <v>1665135.9325000001</v>
       </c>
       <c r="C93" s="20"/>
     </row>
-    <row r="94" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="40"/>
       <c r="C94" s="20"/>
       <c r="D94" s="43"/>
     </row>
-    <row r="95" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="41"/>
       <c r="C95" s="20"/>
     </row>
-    <row r="96" spans="1:5" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="40"/>
       <c r="C96" s="35"/>
     </row>
-    <row r="97" spans="1:13" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="29" t="s">
         <v>54</v>
       </c>
@@ -2680,7 +2699,7 @@
       <c r="C97" s="35"/>
       <c r="D97" s="46"/>
     </row>
-    <row r="98" spans="1:13" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>49</v>
       </c>
@@ -2689,7 +2708,7 @@
       </c>
       <c r="C98" s="35"/>
     </row>
-    <row r="99" spans="1:13" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>55</v>
       </c>
@@ -2699,7 +2718,7 @@
       <c r="C99" s="20"/>
       <c r="D99" s="43"/>
     </row>
-    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>52</v>
       </c>
@@ -2708,7 +2727,7 @@
       </c>
       <c r="C100" s="20"/>
     </row>
-    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>53</v>
       </c>
@@ -2717,7 +2736,7 @@
       </c>
       <c r="C101" s="22"/>
     </row>
-    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="29" t="s">
         <v>56</v>
       </c>
@@ -2727,33 +2746,33 @@
       </c>
       <c r="C102" s="17"/>
     </row>
-    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:13" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A105" s="161" t="s">
+    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="104" spans="1:13" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A105" s="157" t="s">
         <v>57</v>
       </c>
-      <c r="B105" s="155"/>
-      <c r="C105" s="155"/>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A106" s="155"/>
-      <c r="B106" s="155"/>
-      <c r="C106" s="155"/>
-    </row>
-    <row r="107" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="156"/>
+      <c r="C105" s="156"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A106" s="156"/>
+      <c r="B106" s="156"/>
+      <c r="C106" s="156"/>
+    </row>
+    <row r="107" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="55"/>
       <c r="B107" s="33"/>
       <c r="C107" s="33">
         <v>40000</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="55"/>
       <c r="B108" s="33"/>
       <c r="C108" s="40"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="44" t="s">
         <v>36</v>
       </c>
@@ -2763,39 +2782,44 @@
       </c>
       <c r="C109" s="45"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M110" s="8"/>
     </row>
-    <row r="111" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="165"/>
-      <c r="B111" s="155"/>
-      <c r="C111" s="155"/>
-      <c r="D111" s="155"/>
-      <c r="E111" s="155"/>
-    </row>
-    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="155"/>
-      <c r="B112" s="155"/>
-      <c r="C112" s="155"/>
-      <c r="D112" s="155"/>
-      <c r="E112" s="155"/>
-    </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="155"/>
-      <c r="B113" s="155"/>
-      <c r="C113" s="155"/>
-      <c r="D113" s="155"/>
-      <c r="E113" s="155"/>
-    </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="155"/>
-      <c r="B114" s="155"/>
-      <c r="C114" s="155"/>
-      <c r="D114" s="155"/>
-      <c r="E114" s="155"/>
+    <row r="111" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="163"/>
+      <c r="B111" s="156"/>
+      <c r="C111" s="156"/>
+      <c r="D111" s="156"/>
+      <c r="E111" s="156"/>
+    </row>
+    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="156"/>
+      <c r="B112" s="156"/>
+      <c r="C112" s="156"/>
+      <c r="D112" s="156"/>
+      <c r="E112" s="156"/>
+    </row>
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="156"/>
+      <c r="B113" s="156"/>
+      <c r="C113" s="156"/>
+      <c r="D113" s="156"/>
+      <c r="E113" s="156"/>
+    </row>
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="156"/>
+      <c r="B114" s="156"/>
+      <c r="C114" s="156"/>
+      <c r="D114" s="156"/>
+      <c r="E114" s="156"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B9:C11"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A14:E17"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
     <mergeCell ref="A82:E84"/>
     <mergeCell ref="A105:C106"/>
     <mergeCell ref="A69:B69"/>
@@ -2803,11 +2827,6 @@
     <mergeCell ref="A111:E114"/>
     <mergeCell ref="D67:D68"/>
     <mergeCell ref="E67:E68"/>
-    <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A14:E17"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2818,30 +2837,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.109375" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" customWidth="1"/>
+    <col min="11" max="11" width="9.88671875" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" customWidth="1"/>
+    <col min="14" max="14" width="10.5546875" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" customWidth="1"/>
-    <col min="17" max="17" width="4.42578125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" customWidth="1"/>
+    <col min="17" max="17" width="4.44140625" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2849,21 +2868,21 @@
         <v>58</v>
       </c>
       <c r="E1" s="6"/>
-      <c r="F1" s="174" t="s">
+      <c r="F1" s="183" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155"/>
-      <c r="K1" s="155"/>
-      <c r="L1" s="155"/>
-      <c r="M1" s="155"/>
-      <c r="N1" s="155"/>
-      <c r="O1" s="155"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
+      <c r="O1" s="156"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2883,14 +2902,14 @@
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="179">
+      <c r="O2" s="177">
         <f>T4</f>
         <v>4000000</v>
       </c>
-      <c r="P2" s="155"/>
+      <c r="P2" s="156"/>
       <c r="Q2" s="15"/>
     </row>
-    <row r="3" spans="1:20" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -2909,59 +2928,59 @@
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="183">
+      <c r="O3" s="181">
         <f>S6</f>
         <v>181000</v>
       </c>
-      <c r="P3" s="184"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="177" t="s">
+      <c r="P3" s="182"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="171" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="180" t="s">
+      <c r="B4" s="178" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="170" t="s">
+      <c r="C4" s="173" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="170" t="s">
+      <c r="D4" s="173" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="172" t="s">
+      <c r="E4" s="174" t="s">
         <v>67</v>
       </c>
-      <c r="F4" s="170" t="s">
+      <c r="F4" s="173" t="s">
         <v>68</v>
       </c>
-      <c r="G4" s="170" t="s">
+      <c r="G4" s="173" t="s">
         <v>69</v>
       </c>
-      <c r="H4" s="170" t="s">
+      <c r="H4" s="173" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="172" t="s">
+      <c r="I4" s="174" t="s">
         <v>71</v>
       </c>
-      <c r="J4" s="175" t="s">
+      <c r="J4" s="184" t="s">
         <v>72</v>
       </c>
-      <c r="K4" s="178" t="s">
+      <c r="K4" s="176" t="s">
         <v>73</v>
       </c>
-      <c r="L4" s="176" t="s">
+      <c r="L4" s="185" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="178" t="s">
+      <c r="M4" s="176" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="178" t="s">
+      <c r="N4" s="176" t="s">
         <v>76</v>
       </c>
       <c r="O4" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="P4" s="182" t="s">
+      <c r="P4" s="180" t="s">
         <v>78</v>
       </c>
       <c r="S4" s="43"/>
@@ -2969,31 +2988,31 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="171"/>
-      <c r="B5" s="181"/>
-      <c r="C5" s="171"/>
-      <c r="D5" s="171"/>
-      <c r="E5" s="173"/>
-      <c r="F5" s="171"/>
-      <c r="G5" s="171"/>
-      <c r="H5" s="171"/>
-      <c r="I5" s="173"/>
-      <c r="J5" s="173"/>
-      <c r="K5" s="173"/>
-      <c r="L5" s="171"/>
-      <c r="M5" s="173"/>
-      <c r="N5" s="173"/>
+    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="172"/>
+      <c r="B5" s="179"/>
+      <c r="C5" s="172"/>
+      <c r="D5" s="172"/>
+      <c r="E5" s="175"/>
+      <c r="F5" s="172"/>
+      <c r="G5" s="172"/>
+      <c r="H5" s="172"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="175"/>
+      <c r="K5" s="175"/>
+      <c r="L5" s="172"/>
+      <c r="M5" s="175"/>
+      <c r="N5" s="175"/>
       <c r="O5" s="59" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/11</v>
       </c>
-      <c r="P5" s="171"/>
+      <c r="P5" s="172"/>
       <c r="T5" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>79</v>
       </c>
@@ -3056,7 +3075,7 @@
         <v>181000</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>83</v>
       </c>
@@ -3114,7 +3133,7 @@
       </c>
       <c r="R7" s="43"/>
     </row>
-    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>83</v>
       </c>
@@ -3173,7 +3192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>90</v>
       </c>
@@ -3237,7 +3256,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>90</v>
       </c>
@@ -3295,7 +3314,7 @@
       </c>
       <c r="S10" s="43"/>
     </row>
-    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>97</v>
       </c>
@@ -3353,7 +3372,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>97</v>
       </c>
@@ -3413,7 +3432,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>103</v>
       </c>
@@ -3475,66 +3494,69 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="62">
+      <c r="B14" s="186">
         <v>22</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="186" t="s">
         <v>108</v>
       </c>
-      <c r="D14" s="62" t="s">
+      <c r="D14" s="186" t="s">
         <v>109</v>
       </c>
-      <c r="E14" s="62" t="s">
+      <c r="E14" s="186" t="s">
         <v>110</v>
       </c>
-      <c r="F14" s="68">
+      <c r="F14" s="187">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G14" s="133">
-        <v>2196288.2200000002</v>
-      </c>
-      <c r="H14" s="69">
+      <c r="G14" s="188">
         <v>213231.22</v>
       </c>
-      <c r="I14" s="70"/>
-      <c r="J14" s="117">
+      <c r="H14" s="189">
+        <v>215000</v>
+      </c>
+      <c r="I14" s="190"/>
+      <c r="J14" s="191">
         <f t="shared" si="0"/>
-        <v>1983057.0000000002</v>
-      </c>
-      <c r="K14" s="71">
+        <v>-1768.7799999999988</v>
+      </c>
+      <c r="K14" s="191">
         <f t="shared" si="1"/>
-        <v>99152.85000000002</v>
-      </c>
-      <c r="L14" s="72">
+        <v>0</v>
+      </c>
+      <c r="L14" s="192">
         <f t="shared" si="2"/>
         <v>9231</v>
       </c>
-      <c r="M14" s="72">
+      <c r="M14" s="192">
         <f t="shared" si="3"/>
         <v>204000</v>
       </c>
-      <c r="N14" s="114">
+      <c r="N14" s="193">
         <f t="shared" si="4"/>
-        <v>2295440.8500000006</v>
-      </c>
-      <c r="O14" s="116" t="str">
+        <v>211462.22</v>
+      </c>
+      <c r="O14" s="194" t="str">
         <f t="shared" si="5"/>
-        <v>$2295441,22</v>
-      </c>
-      <c r="P14" s="119" t="str">
+        <v>$211462,22</v>
+      </c>
+      <c r="P14" s="195" t="str">
         <f t="shared" si="6"/>
-        <v>$2364304,22</v>
+        <v>$217806,22</v>
       </c>
       <c r="Q14" s="43" t="str">
         <f t="shared" si="7"/>
         <v>22</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>111</v>
       </c>
@@ -3592,7 +3614,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>111</v>
       </c>
@@ -3652,7 +3674,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>117</v>
       </c>
@@ -3709,7 +3731,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>117</v>
       </c>
@@ -3768,7 +3790,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>123</v>
       </c>
@@ -3823,7 +3845,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>123</v>
       </c>
@@ -3886,7 +3908,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>128</v>
       </c>
@@ -3945,7 +3967,7 @@
       </c>
       <c r="S21" s="42"/>
     </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>128</v>
       </c>
@@ -4006,7 +4028,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>134</v>
       </c>
@@ -4069,7 +4091,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>134</v>
       </c>
@@ -4130,7 +4152,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="73"/>
       <c r="C25" s="74"/>
       <c r="D25" s="75"/>
@@ -4141,11 +4163,11 @@
       </c>
       <c r="G25" s="54">
         <f t="shared" si="8"/>
-        <v>35610063.899999991</v>
+        <v>33627006.899999999</v>
       </c>
       <c r="H25" s="60">
         <f t="shared" si="8"/>
-        <v>4082670.82</v>
+        <v>4084439.6</v>
       </c>
       <c r="I25" s="54">
         <f t="shared" si="8"/>
@@ -4153,11 +4175,11 @@
       </c>
       <c r="J25" s="60">
         <f t="shared" si="8"/>
-        <v>31527393.080000002</v>
+        <v>29542567.300000001</v>
       </c>
       <c r="K25" s="60">
         <f t="shared" si="8"/>
-        <v>1576711.2960000001</v>
+        <v>1477558.446</v>
       </c>
       <c r="L25" s="60">
         <f t="shared" si="8"/>
@@ -4177,97 +4199,97 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D26" s="51"/>
       <c r="E26" s="51"/>
       <c r="R26" s="104"/>
     </row>
-    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="165" t="s">
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D28" s="163" t="s">
         <v>140</v>
       </c>
-      <c r="E28" s="155"/>
-      <c r="F28" s="155"/>
-      <c r="G28" s="155"/>
-      <c r="H28" s="155"/>
-      <c r="I28" s="155"/>
-      <c r="J28" s="155"/>
-      <c r="K28" s="155"/>
-      <c r="L28" s="155"/>
-      <c r="M28" s="155"/>
-      <c r="N28" s="155"/>
-      <c r="O28" s="155"/>
-    </row>
-    <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D29" s="155"/>
-      <c r="E29" s="155"/>
-      <c r="F29" s="155"/>
-      <c r="G29" s="155"/>
-      <c r="H29" s="155"/>
-      <c r="I29" s="155"/>
-      <c r="J29" s="155"/>
-      <c r="K29" s="155"/>
-      <c r="L29" s="155"/>
-      <c r="M29" s="155"/>
-      <c r="N29" s="155"/>
-      <c r="O29" s="155"/>
-    </row>
-    <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="155"/>
-      <c r="E30" s="155"/>
-      <c r="F30" s="155"/>
-      <c r="G30" s="155"/>
-      <c r="H30" s="155"/>
-      <c r="I30" s="155"/>
-      <c r="J30" s="155"/>
-      <c r="K30" s="155"/>
-      <c r="L30" s="155"/>
-      <c r="M30" s="155"/>
-      <c r="N30" s="155"/>
-      <c r="O30" s="155"/>
-    </row>
-    <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="155"/>
-      <c r="E31" s="155"/>
-      <c r="F31" s="155"/>
-      <c r="G31" s="155"/>
-      <c r="H31" s="155"/>
-      <c r="I31" s="155"/>
-      <c r="J31" s="155"/>
-      <c r="K31" s="155"/>
-      <c r="L31" s="155"/>
-      <c r="M31" s="155"/>
-      <c r="N31" s="155"/>
-      <c r="O31" s="155"/>
-    </row>
-    <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D32" s="155"/>
-      <c r="E32" s="155"/>
-      <c r="F32" s="155"/>
-      <c r="G32" s="155"/>
-      <c r="H32" s="155"/>
-      <c r="I32" s="155"/>
-      <c r="J32" s="155"/>
-      <c r="K32" s="155"/>
-      <c r="L32" s="155"/>
-      <c r="M32" s="155"/>
-      <c r="N32" s="155"/>
-      <c r="O32" s="155"/>
-    </row>
-    <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="155"/>
-      <c r="E33" s="155"/>
-      <c r="F33" s="155"/>
-      <c r="G33" s="155"/>
-      <c r="H33" s="155"/>
-      <c r="I33" s="155"/>
-      <c r="J33" s="155"/>
-      <c r="K33" s="155"/>
-      <c r="L33" s="155"/>
-      <c r="M33" s="155"/>
-      <c r="N33" s="155"/>
-      <c r="O33" s="155"/>
+      <c r="E28" s="156"/>
+      <c r="F28" s="156"/>
+      <c r="G28" s="156"/>
+      <c r="H28" s="156"/>
+      <c r="I28" s="156"/>
+      <c r="J28" s="156"/>
+      <c r="K28" s="156"/>
+      <c r="L28" s="156"/>
+      <c r="M28" s="156"/>
+      <c r="N28" s="156"/>
+      <c r="O28" s="156"/>
+    </row>
+    <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D29" s="156"/>
+      <c r="E29" s="156"/>
+      <c r="F29" s="156"/>
+      <c r="G29" s="156"/>
+      <c r="H29" s="156"/>
+      <c r="I29" s="156"/>
+      <c r="J29" s="156"/>
+      <c r="K29" s="156"/>
+      <c r="L29" s="156"/>
+      <c r="M29" s="156"/>
+      <c r="N29" s="156"/>
+      <c r="O29" s="156"/>
+    </row>
+    <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D30" s="156"/>
+      <c r="E30" s="156"/>
+      <c r="F30" s="156"/>
+      <c r="G30" s="156"/>
+      <c r="H30" s="156"/>
+      <c r="I30" s="156"/>
+      <c r="J30" s="156"/>
+      <c r="K30" s="156"/>
+      <c r="L30" s="156"/>
+      <c r="M30" s="156"/>
+      <c r="N30" s="156"/>
+      <c r="O30" s="156"/>
+    </row>
+    <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D31" s="156"/>
+      <c r="E31" s="156"/>
+      <c r="F31" s="156"/>
+      <c r="G31" s="156"/>
+      <c r="H31" s="156"/>
+      <c r="I31" s="156"/>
+      <c r="J31" s="156"/>
+      <c r="K31" s="156"/>
+      <c r="L31" s="156"/>
+      <c r="M31" s="156"/>
+      <c r="N31" s="156"/>
+      <c r="O31" s="156"/>
+    </row>
+    <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D32" s="156"/>
+      <c r="E32" s="156"/>
+      <c r="F32" s="156"/>
+      <c r="G32" s="156"/>
+      <c r="H32" s="156"/>
+      <c r="I32" s="156"/>
+      <c r="J32" s="156"/>
+      <c r="K32" s="156"/>
+      <c r="L32" s="156"/>
+      <c r="M32" s="156"/>
+      <c r="N32" s="156"/>
+      <c r="O32" s="156"/>
+    </row>
+    <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D33" s="156"/>
+      <c r="E33" s="156"/>
+      <c r="F33" s="156"/>
+      <c r="G33" s="156"/>
+      <c r="H33" s="156"/>
+      <c r="I33" s="156"/>
+      <c r="J33" s="156"/>
+      <c r="K33" s="156"/>
+      <c r="L33" s="156"/>
+      <c r="M33" s="156"/>
+      <c r="N33" s="156"/>
+      <c r="O33" s="156"/>
       <c r="R33" s="104"/>
       <c r="S33" s="104"/>
       <c r="T33" s="104"/>
@@ -4275,6 +4297,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="D28:O33"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F1:O1"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:L5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
@@ -4287,13 +4316,6 @@
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="O3:P3"/>
-    <mergeCell ref="D28:O33"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F1:O1"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
